--- a/Calibration Template USD.xlsx
+++ b/Calibration Template USD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://people.ey.com/personal/pablo_marchesi_selma_es_ey_com/Documents/Desktop/Calculadoras/HW/HW_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://people.ey.com/personal/pablo_marchesi_selma_es_ey_com/Documents/Desktop/Calculadoras/Hull-White-Pricer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{00F85499-E803-408C-8FFB-B6A833A2FC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F35A909B-0F10-4E17-A715-24AEFF15E8C2}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="8_{00F85499-E803-408C-8FFB-B6A833A2FC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF86FC71-76AA-41B1-A23F-4E7BF040D9C9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,9 +624,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -646,17 +643,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1584,19 +1584,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="44" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1605,11 +1605,11 @@
         <f>MAX('CAP1'!J3:J5)</f>
         <v>2</v>
       </c>
-      <c r="B2" s="48">
-        <f>'CAP1'!D3/100</f>
-        <v>3.7080962781537302E-2</v>
-      </c>
-      <c r="C2" s="41">
+      <c r="B2" s="47">
+        <f>'CAP1'!D3</f>
+        <v>3.7080962781537301</v>
+      </c>
+      <c r="C2" s="40">
         <f>'CAP1'!I3</f>
         <v>1000000</v>
       </c>
@@ -1621,14 +1621,14 @@
         <f t="shared" ref="E2:E6" si="0">G2-F2</f>
         <v>0.5</v>
       </c>
-      <c r="F2" s="43" cm="1">
+      <c r="F2" s="42" cm="1">
         <f t="array" ref="F2:H2">TRANSPOSE('CAP1'!J3:J5)</f>
         <v>1</v>
       </c>
-      <c r="G2" s="43">
+      <c r="G2" s="42">
         <v>1.5</v>
       </c>
-      <c r="H2" s="44">
+      <c r="H2" s="43">
         <v>2</v>
       </c>
     </row>
@@ -1637,11 +1637,11 @@
         <f>MAX('CAP2'!J3:J7)</f>
         <v>3</v>
       </c>
-      <c r="B3" s="46">
-        <f>'CAP2'!D3/100</f>
-        <v>3.6405459997168002E-2</v>
-      </c>
-      <c r="C3" s="47">
+      <c r="B3" s="48">
+        <f>'CAP2'!D3</f>
+        <v>3.6405459997167999</v>
+      </c>
+      <c r="C3" s="45">
         <f>'CAP2'!I3</f>
         <v>1000000</v>
       </c>
@@ -1669,51 +1669,51 @@
       <c r="J3" s="30">
         <v>3</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="42"/>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="42"/>
-      <c r="AE3" s="42"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="42"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="42"/>
-      <c r="AK3" s="42"/>
-      <c r="AL3" s="42"/>
-      <c r="AM3" s="42"/>
-      <c r="AN3" s="42"/>
-      <c r="AO3" s="42"/>
-      <c r="AP3" s="42"/>
-      <c r="AQ3" s="42"/>
-      <c r="AR3" s="42"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="41"/>
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41"/>
+      <c r="AN3" s="41"/>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="41"/>
+      <c r="AR3" s="41"/>
     </row>
     <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="39">
+      <c r="A4" s="38">
         <f>MAX('CAP3'!J3:J11)</f>
         <v>4.9972222222222218</v>
       </c>
-      <c r="B4" s="38">
-        <f>'CAP3'!D3/100</f>
-        <v>3.6414804986144703E-2</v>
-      </c>
-      <c r="C4" s="40">
+      <c r="B4" s="49">
+        <f>'CAP3'!D3</f>
+        <v>3.6414804986144702</v>
+      </c>
+      <c r="C4" s="39">
         <f>'CAP3'!I3</f>
         <v>1000000</v>
       </c>
@@ -1753,47 +1753,47 @@
       <c r="N4" s="30">
         <v>4.9972222222222218</v>
       </c>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="42"/>
-      <c r="V4" s="42"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="42"/>
-      <c r="Y4" s="42"/>
-      <c r="Z4" s="42"/>
-      <c r="AA4" s="42"/>
-      <c r="AB4" s="42"/>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="42"/>
-      <c r="AE4" s="42"/>
-      <c r="AF4" s="42"/>
-      <c r="AG4" s="42"/>
-      <c r="AH4" s="42"/>
-      <c r="AI4" s="42"/>
-      <c r="AJ4" s="42"/>
-      <c r="AK4" s="42"/>
-      <c r="AL4" s="42"/>
-      <c r="AM4" s="42"/>
-      <c r="AN4" s="42"/>
-      <c r="AO4" s="42"/>
-      <c r="AP4" s="42"/>
-      <c r="AQ4" s="42"/>
-      <c r="AR4" s="42"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="41"/>
+      <c r="AJ4" s="41"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
     </row>
     <row r="5" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <f>MAX('CAP4'!J3:J21)</f>
         <v>10</v>
       </c>
-      <c r="B5" s="38">
-        <f>'CAP4'!D3/100</f>
-        <v>3.7588216849118901E-2</v>
-      </c>
-      <c r="C5" s="40">
+      <c r="B5" s="49">
+        <f>'CAP4'!D3</f>
+        <v>3.7588216849118901</v>
+      </c>
+      <c r="C5" s="39">
         <f>'CAP5'!I3</f>
         <v>1000000</v>
       </c>
@@ -1863,37 +1863,37 @@
       <c r="X5" s="30">
         <v>10</v>
       </c>
-      <c r="Y5" s="42"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="42"/>
-      <c r="AB5" s="42"/>
-      <c r="AC5" s="42"/>
-      <c r="AD5" s="42"/>
-      <c r="AE5" s="42"/>
-      <c r="AF5" s="42"/>
-      <c r="AG5" s="42"/>
-      <c r="AH5" s="42"/>
-      <c r="AI5" s="42"/>
-      <c r="AJ5" s="42"/>
-      <c r="AK5" s="42"/>
-      <c r="AL5" s="42"/>
-      <c r="AM5" s="42"/>
-      <c r="AN5" s="42"/>
-      <c r="AO5" s="42"/>
-      <c r="AP5" s="42"/>
-      <c r="AQ5" s="42"/>
-      <c r="AR5" s="42"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="41"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="41"/>
     </row>
     <row r="6" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="37">
         <f>MAX('CAP5'!J3:J41)</f>
         <v>20</v>
       </c>
-      <c r="B6" s="48">
-        <f>'CAP5'!D3/100</f>
-        <v>3.8923013975015498E-2</v>
-      </c>
-      <c r="C6" s="41">
+      <c r="B6" s="47">
+        <f>'CAP5'!D3</f>
+        <v>3.8923013975015501</v>
+      </c>
+      <c r="C6" s="40">
         <f>'CAP5'!I3</f>
         <v>1000000</v>
       </c>
@@ -1905,122 +1905,122 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F6" s="43" cm="1">
+      <c r="F6" s="42" cm="1">
         <f t="array" ref="F6:AR6">TRANSPOSE('CAP5'!J3:J41)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="42">
         <v>1.5</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="42">
         <v>2</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="42">
         <v>2.5</v>
       </c>
-      <c r="J6" s="43">
+      <c r="J6" s="42">
         <v>3</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="42">
         <v>3.4972222222222222</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="42">
         <v>4</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="42">
         <v>4.4944444444444445</v>
       </c>
-      <c r="N6" s="43">
+      <c r="N6" s="42">
         <v>4.9972222222222218</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="42">
         <v>5.5</v>
       </c>
-      <c r="P6" s="43">
+      <c r="P6" s="42">
         <v>6</v>
       </c>
-      <c r="Q6" s="43">
+      <c r="Q6" s="42">
         <v>6.5</v>
       </c>
-      <c r="R6" s="43">
+      <c r="R6" s="42">
         <v>7</v>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="42">
         <v>7.5</v>
       </c>
-      <c r="T6" s="43">
+      <c r="T6" s="42">
         <v>8</v>
       </c>
-      <c r="U6" s="43">
+      <c r="U6" s="42">
         <v>8.5</v>
       </c>
-      <c r="V6" s="43">
+      <c r="V6" s="42">
         <v>9</v>
       </c>
-      <c r="W6" s="43">
+      <c r="W6" s="42">
         <v>9.4972222222222218</v>
       </c>
-      <c r="X6" s="43">
+      <c r="X6" s="42">
         <v>10</v>
       </c>
-      <c r="Y6" s="43">
+      <c r="Y6" s="42">
         <v>10.494444444444444</v>
       </c>
-      <c r="Z6" s="43">
+      <c r="Z6" s="42">
         <v>11</v>
       </c>
-      <c r="AA6" s="43">
+      <c r="AA6" s="42">
         <v>11.5</v>
       </c>
-      <c r="AB6" s="43">
+      <c r="AB6" s="42">
         <v>12</v>
       </c>
-      <c r="AC6" s="43">
+      <c r="AC6" s="42">
         <v>12.5</v>
       </c>
-      <c r="AD6" s="43">
+      <c r="AD6" s="42">
         <v>13</v>
       </c>
-      <c r="AE6" s="43">
+      <c r="AE6" s="42">
         <v>13.5</v>
       </c>
-      <c r="AF6" s="43">
+      <c r="AF6" s="42">
         <v>14</v>
       </c>
-      <c r="AG6" s="43">
+      <c r="AG6" s="42">
         <v>14.5</v>
       </c>
-      <c r="AH6" s="43">
+      <c r="AH6" s="42">
         <v>15</v>
       </c>
-      <c r="AI6" s="43">
+      <c r="AI6" s="42">
         <v>15.494444444444444</v>
       </c>
-      <c r="AJ6" s="43">
+      <c r="AJ6" s="42">
         <v>15.997222222222222</v>
       </c>
-      <c r="AK6" s="43">
+      <c r="AK6" s="42">
         <v>16.5</v>
       </c>
-      <c r="AL6" s="43">
+      <c r="AL6" s="42">
         <v>17</v>
       </c>
-      <c r="AM6" s="43">
+      <c r="AM6" s="42">
         <v>17.5</v>
       </c>
-      <c r="AN6" s="43">
+      <c r="AN6" s="42">
         <v>18</v>
       </c>
-      <c r="AO6" s="43">
+      <c r="AO6" s="42">
         <v>18.5</v>
       </c>
-      <c r="AP6" s="43">
+      <c r="AP6" s="42">
         <v>19</v>
       </c>
-      <c r="AQ6" s="43">
+      <c r="AQ6" s="42">
         <v>19.5</v>
       </c>
-      <c r="AR6" s="44">
+      <c r="AR6" s="43">
         <v>20</v>
       </c>
     </row>
@@ -2045,28 +2045,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="46" t="s">
         <v>48</v>
       </c>
       <c r="J2" s="36" t="s">
@@ -2108,28 +2108,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="46" t="s">
         <v>48</v>
       </c>
       <c r="J2" s="36" t="s">

--- a/Calibration Template USD.xlsx
+++ b/Calibration Template USD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://people.ey.com/personal/pablo_marchesi_selma_es_ey_com/Documents/Desktop/Calculadoras/Hull-White-Pricer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="8_{00F85499-E803-408C-8FFB-B6A833A2FC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF86FC71-76AA-41B1-A23F-4E7BF040D9C9}"/>
+  <xr:revisionPtr revIDLastSave="312" documentId="8_{00F85499-E803-408C-8FFB-B6A833A2FC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59A869A5-BFA3-45A5-BE59-F5A0B06A7B72}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curve" sheetId="2" r:id="rId1"/>
@@ -1514,57 +1514,32 @@
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="13">
-        <f t="shared" si="0"/>
-        <v>125.25277777777778</v>
-      </c>
-      <c r="D35" s="8">
-        <v>0.520305723557551</v>
-      </c>
+      <c r="C35" s="13"/>
+      <c r="D35" s="8"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="13">
-        <f t="shared" si="0"/>
-        <v>125.25277777777778</v>
-      </c>
-      <c r="D36" s="8">
-        <v>0.468168168315861</v>
-      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="13">
-        <f t="shared" si="0"/>
-        <v>125.25277777777778</v>
-      </c>
-      <c r="D37" s="8">
-        <v>0.37848081579099802</v>
-      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="13">
-        <f t="shared" si="0"/>
-        <v>125.25277777777778</v>
-      </c>
-      <c r="D38" s="8">
-        <v>0.31292981348091498</v>
-      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="9"/>
       <c r="B39" s="10"/>
-      <c r="C39" s="14">
-        <f t="shared" si="0"/>
-        <v>125.25277777777778</v>
-      </c>
-      <c r="D39" s="11">
-        <v>0.26963699121603801</v>
-      </c>
+      <c r="C39" s="14"/>
+      <c r="D39" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
